--- a/pedidos/F2026020S.xlsx
+++ b/pedidos/F2026020S.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Agroserver\libs_analise\01_Comerciais\05) ATVOS\2027-07-27 - Remessa20\07_Referencias_Quimico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agroroboticafca-my.sharepoint.com/personal/miguel_santos_agrorobotica_com_br/Documents/AGROROBOTICA/PROJETOS/Dashoboard_ATVOS/pedidos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851B356C-092F-4B43-9A38-918BB11F75CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{851B356C-092F-4B43-9A38-918BB11F75CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B1F317C-05E6-404A-A45A-710180C3404A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1471,11 +1471,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2072,6 +2073,9 @@
       <c r="D2" t="s">
         <v>61</v>
       </c>
+      <c r="E2" s="2">
+        <v>46230</v>
+      </c>
       <c r="F2" t="s">
         <v>62</v>
       </c>
@@ -2185,6 +2189,9 @@
       <c r="D3" t="s">
         <v>61</v>
       </c>
+      <c r="E3" s="2">
+        <v>46230</v>
+      </c>
       <c r="F3" t="s">
         <v>62</v>
       </c>
@@ -2298,6 +2305,9 @@
       <c r="D4" t="s">
         <v>61</v>
       </c>
+      <c r="E4" s="2">
+        <v>46230</v>
+      </c>
       <c r="F4" t="s">
         <v>62</v>
       </c>
@@ -2410,6 +2420,9 @@
       </c>
       <c r="D5" t="s">
         <v>61</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46230</v>
       </c>
       <c r="F5" t="s">
         <v>62</v>
@@ -2521,6 +2534,9 @@
       <c r="D6" t="s">
         <v>74</v>
       </c>
+      <c r="E6" s="2">
+        <v>46230</v>
+      </c>
       <c r="F6" t="s">
         <v>75</v>
       </c>
@@ -2634,6 +2650,9 @@
       <c r="D7" t="s">
         <v>74</v>
       </c>
+      <c r="E7" s="2">
+        <v>46230</v>
+      </c>
       <c r="F7" t="s">
         <v>75</v>
       </c>
@@ -2747,6 +2766,9 @@
       <c r="D8" t="s">
         <v>78</v>
       </c>
+      <c r="E8" s="2">
+        <v>46230</v>
+      </c>
       <c r="F8" t="s">
         <v>75</v>
       </c>
@@ -2860,6 +2882,9 @@
       <c r="D9" t="s">
         <v>78</v>
       </c>
+      <c r="E9" s="2">
+        <v>46230</v>
+      </c>
       <c r="F9" t="s">
         <v>75</v>
       </c>
@@ -2973,6 +2998,9 @@
       <c r="D10" t="s">
         <v>81</v>
       </c>
+      <c r="E10" s="2">
+        <v>46230</v>
+      </c>
       <c r="F10" t="s">
         <v>75</v>
       </c>
@@ -3086,6 +3114,9 @@
       <c r="D11" t="s">
         <v>81</v>
       </c>
+      <c r="E11" s="2">
+        <v>46230</v>
+      </c>
       <c r="F11" t="s">
         <v>75</v>
       </c>
@@ -3196,6 +3227,9 @@
       <c r="D12" t="s">
         <v>84</v>
       </c>
+      <c r="E12" s="2">
+        <v>46230</v>
+      </c>
       <c r="F12" t="s">
         <v>75</v>
       </c>
@@ -3306,6 +3340,9 @@
       <c r="D13" t="s">
         <v>84</v>
       </c>
+      <c r="E13" s="2">
+        <v>46230</v>
+      </c>
       <c r="F13" t="s">
         <v>75</v>
       </c>
@@ -3416,6 +3453,9 @@
       <c r="D14" t="s">
         <v>87</v>
       </c>
+      <c r="E14" s="2">
+        <v>46230</v>
+      </c>
       <c r="F14" t="s">
         <v>75</v>
       </c>
@@ -3529,6 +3569,9 @@
       <c r="D15" t="s">
         <v>87</v>
       </c>
+      <c r="E15" s="2">
+        <v>46230</v>
+      </c>
       <c r="F15" t="s">
         <v>75</v>
       </c>
@@ -3639,6 +3682,9 @@
       <c r="D16" t="s">
         <v>90</v>
       </c>
+      <c r="E16" s="2">
+        <v>46230</v>
+      </c>
       <c r="F16" t="s">
         <v>91</v>
       </c>
@@ -3752,6 +3798,9 @@
       <c r="D17" t="s">
         <v>90</v>
       </c>
+      <c r="E17" s="2">
+        <v>46230</v>
+      </c>
       <c r="F17" t="s">
         <v>91</v>
       </c>
@@ -3865,6 +3914,9 @@
       <c r="D18" t="s">
         <v>94</v>
       </c>
+      <c r="E18" s="2">
+        <v>46230</v>
+      </c>
       <c r="F18" t="s">
         <v>91</v>
       </c>
@@ -3978,6 +4030,9 @@
       <c r="D19" t="s">
         <v>94</v>
       </c>
+      <c r="E19" s="2">
+        <v>46230</v>
+      </c>
       <c r="F19" t="s">
         <v>91</v>
       </c>
@@ -4088,6 +4143,9 @@
       <c r="D20" t="s">
         <v>97</v>
       </c>
+      <c r="E20" s="2">
+        <v>46230</v>
+      </c>
       <c r="F20" t="s">
         <v>91</v>
       </c>
@@ -4198,6 +4256,9 @@
       <c r="D21" t="s">
         <v>97</v>
       </c>
+      <c r="E21" s="2">
+        <v>46230</v>
+      </c>
       <c r="F21" t="s">
         <v>91</v>
       </c>
@@ -4308,6 +4369,9 @@
       <c r="D22" t="s">
         <v>100</v>
       </c>
+      <c r="E22" s="2">
+        <v>46230</v>
+      </c>
       <c r="F22" t="s">
         <v>91</v>
       </c>
@@ -4418,6 +4482,9 @@
       <c r="D23" t="s">
         <v>100</v>
       </c>
+      <c r="E23" s="2">
+        <v>46230</v>
+      </c>
       <c r="F23" t="s">
         <v>91</v>
       </c>
@@ -4528,6 +4595,9 @@
       <c r="D24" t="s">
         <v>103</v>
       </c>
+      <c r="E24" s="2">
+        <v>46230</v>
+      </c>
       <c r="F24" t="s">
         <v>91</v>
       </c>
@@ -4641,6 +4711,9 @@
       <c r="D25" t="s">
         <v>103</v>
       </c>
+      <c r="E25" s="2">
+        <v>46230</v>
+      </c>
       <c r="F25" t="s">
         <v>91</v>
       </c>
@@ -4751,6 +4824,9 @@
       <c r="D26" t="s">
         <v>106</v>
       </c>
+      <c r="E26" s="2">
+        <v>46230</v>
+      </c>
       <c r="F26" t="s">
         <v>91</v>
       </c>
@@ -4861,6 +4937,9 @@
       <c r="D27" t="s">
         <v>106</v>
       </c>
+      <c r="E27" s="2">
+        <v>46230</v>
+      </c>
       <c r="F27" t="s">
         <v>91</v>
       </c>
@@ -4971,6 +5050,9 @@
       <c r="D28" t="s">
         <v>109</v>
       </c>
+      <c r="E28" s="2">
+        <v>46230</v>
+      </c>
       <c r="F28" t="s">
         <v>91</v>
       </c>
@@ -5084,6 +5166,9 @@
       <c r="D29" t="s">
         <v>109</v>
       </c>
+      <c r="E29" s="2">
+        <v>46230</v>
+      </c>
       <c r="F29" t="s">
         <v>91</v>
       </c>
@@ -5194,6 +5279,9 @@
       <c r="D30" t="s">
         <v>112</v>
       </c>
+      <c r="E30" s="2">
+        <v>46230</v>
+      </c>
       <c r="F30" t="s">
         <v>62</v>
       </c>
@@ -5307,6 +5395,9 @@
       <c r="D31" t="s">
         <v>112</v>
       </c>
+      <c r="E31" s="2">
+        <v>46230</v>
+      </c>
       <c r="F31" t="s">
         <v>62</v>
       </c>
@@ -5420,6 +5511,9 @@
       <c r="D32" t="s">
         <v>115</v>
       </c>
+      <c r="E32" s="2">
+        <v>46230</v>
+      </c>
       <c r="F32" t="s">
         <v>62</v>
       </c>
@@ -5533,6 +5627,9 @@
       <c r="D33" t="s">
         <v>115</v>
       </c>
+      <c r="E33" s="2">
+        <v>46230</v>
+      </c>
       <c r="F33" t="s">
         <v>62</v>
       </c>
@@ -5643,6 +5740,9 @@
       <c r="D34" t="s">
         <v>118</v>
       </c>
+      <c r="E34" s="2">
+        <v>46230</v>
+      </c>
       <c r="F34" t="s">
         <v>62</v>
       </c>
@@ -5753,6 +5853,9 @@
       <c r="D35" t="s">
         <v>118</v>
       </c>
+      <c r="E35" s="2">
+        <v>46230</v>
+      </c>
       <c r="F35" t="s">
         <v>62</v>
       </c>
@@ -5863,6 +5966,9 @@
       <c r="D36" t="s">
         <v>121</v>
       </c>
+      <c r="E36" s="2">
+        <v>46230</v>
+      </c>
       <c r="F36" t="s">
         <v>75</v>
       </c>
@@ -5976,6 +6082,9 @@
       <c r="D37" t="s">
         <v>121</v>
       </c>
+      <c r="E37" s="2">
+        <v>46230</v>
+      </c>
       <c r="F37" t="s">
         <v>75</v>
       </c>
@@ -6089,6 +6198,9 @@
       <c r="D38" t="s">
         <v>124</v>
       </c>
+      <c r="E38" s="2">
+        <v>46230</v>
+      </c>
       <c r="F38" t="s">
         <v>75</v>
       </c>
@@ -6202,6 +6314,9 @@
       <c r="D39" t="s">
         <v>124</v>
       </c>
+      <c r="E39" s="2">
+        <v>46230</v>
+      </c>
       <c r="F39" t="s">
         <v>75</v>
       </c>
@@ -6312,6 +6427,9 @@
       <c r="D40" t="s">
         <v>127</v>
       </c>
+      <c r="E40" s="2">
+        <v>46230</v>
+      </c>
       <c r="F40" t="s">
         <v>75</v>
       </c>
@@ -6422,6 +6540,9 @@
       <c r="D41" t="s">
         <v>127</v>
       </c>
+      <c r="E41" s="2">
+        <v>46230</v>
+      </c>
       <c r="F41" t="s">
         <v>75</v>
       </c>
@@ -6532,6 +6653,9 @@
       <c r="D42" t="s">
         <v>130</v>
       </c>
+      <c r="E42" s="2">
+        <v>46230</v>
+      </c>
       <c r="F42" t="s">
         <v>75</v>
       </c>
@@ -6645,6 +6769,9 @@
       <c r="D43" t="s">
         <v>130</v>
       </c>
+      <c r="E43" s="2">
+        <v>46230</v>
+      </c>
       <c r="F43" t="s">
         <v>75</v>
       </c>
@@ -6755,6 +6882,9 @@
       <c r="D44" t="s">
         <v>133</v>
       </c>
+      <c r="E44" s="2">
+        <v>46230</v>
+      </c>
       <c r="F44" t="s">
         <v>75</v>
       </c>
@@ -6865,6 +6995,9 @@
       <c r="D45" t="s">
         <v>133</v>
       </c>
+      <c r="E45" s="2">
+        <v>46230</v>
+      </c>
       <c r="F45" t="s">
         <v>75</v>
       </c>
@@ -6975,6 +7108,9 @@
       <c r="D46" t="s">
         <v>136</v>
       </c>
+      <c r="E46" s="2">
+        <v>46230</v>
+      </c>
       <c r="F46" t="s">
         <v>75</v>
       </c>
@@ -7088,6 +7224,9 @@
       <c r="D47" t="s">
         <v>136</v>
       </c>
+      <c r="E47" s="2">
+        <v>46230</v>
+      </c>
       <c r="F47" t="s">
         <v>75</v>
       </c>
@@ -7198,6 +7337,9 @@
       <c r="D48" t="s">
         <v>139</v>
       </c>
+      <c r="E48" s="2">
+        <v>46230</v>
+      </c>
       <c r="F48" t="s">
         <v>75</v>
       </c>
@@ -7308,6 +7450,9 @@
       <c r="D49" t="s">
         <v>139</v>
       </c>
+      <c r="E49" s="2">
+        <v>46230</v>
+      </c>
       <c r="F49" t="s">
         <v>75</v>
       </c>
@@ -7418,6 +7563,9 @@
       <c r="D50" t="s">
         <v>142</v>
       </c>
+      <c r="E50" s="2">
+        <v>46230</v>
+      </c>
       <c r="F50" t="s">
         <v>75</v>
       </c>
@@ -7528,6 +7676,9 @@
       <c r="D51" t="s">
         <v>142</v>
       </c>
+      <c r="E51" s="2">
+        <v>46230</v>
+      </c>
       <c r="F51" t="s">
         <v>75</v>
       </c>
@@ -7638,6 +7789,9 @@
       <c r="D52" t="s">
         <v>145</v>
       </c>
+      <c r="E52" s="2">
+        <v>46230</v>
+      </c>
       <c r="F52" t="s">
         <v>75</v>
       </c>
@@ -7748,6 +7902,9 @@
       <c r="D53" t="s">
         <v>145</v>
       </c>
+      <c r="E53" s="2">
+        <v>46230</v>
+      </c>
       <c r="F53" t="s">
         <v>75</v>
       </c>
@@ -7858,6 +8015,9 @@
       <c r="D54" t="s">
         <v>148</v>
       </c>
+      <c r="E54" s="2">
+        <v>46230</v>
+      </c>
       <c r="F54" t="s">
         <v>75</v>
       </c>
@@ -7968,6 +8128,9 @@
       <c r="D55" t="s">
         <v>148</v>
       </c>
+      <c r="E55" s="2">
+        <v>46230</v>
+      </c>
       <c r="F55" t="s">
         <v>75</v>
       </c>
@@ -8078,6 +8241,9 @@
       <c r="D56" t="s">
         <v>151</v>
       </c>
+      <c r="E56" s="2">
+        <v>46230</v>
+      </c>
       <c r="F56" t="s">
         <v>75</v>
       </c>
@@ -8191,6 +8357,9 @@
       <c r="D57" t="s">
         <v>151</v>
       </c>
+      <c r="E57" s="2">
+        <v>46230</v>
+      </c>
       <c r="F57" t="s">
         <v>75</v>
       </c>
@@ -8301,6 +8470,9 @@
       <c r="D58" t="s">
         <v>154</v>
       </c>
+      <c r="E58" s="2">
+        <v>46230</v>
+      </c>
       <c r="F58" t="s">
         <v>75</v>
       </c>
@@ -8414,6 +8586,9 @@
       <c r="D59" t="s">
         <v>154</v>
       </c>
+      <c r="E59" s="2">
+        <v>46230</v>
+      </c>
       <c r="F59" t="s">
         <v>75</v>
       </c>
@@ -8524,6 +8699,9 @@
       <c r="D60" t="s">
         <v>157</v>
       </c>
+      <c r="E60" s="2">
+        <v>46230</v>
+      </c>
       <c r="F60" t="s">
         <v>75</v>
       </c>
@@ -8634,6 +8812,9 @@
       <c r="D61" t="s">
         <v>157</v>
       </c>
+      <c r="E61" s="2">
+        <v>46230</v>
+      </c>
       <c r="F61" t="s">
         <v>75</v>
       </c>
@@ -8744,6 +8925,9 @@
       <c r="D62" t="s">
         <v>160</v>
       </c>
+      <c r="E62" s="2">
+        <v>46230</v>
+      </c>
       <c r="F62" t="s">
         <v>75</v>
       </c>
@@ -8854,6 +9038,9 @@
       <c r="D63" t="s">
         <v>160</v>
       </c>
+      <c r="E63" s="2">
+        <v>46230</v>
+      </c>
       <c r="F63" t="s">
         <v>75</v>
       </c>
@@ -8964,6 +9151,9 @@
       <c r="D64" t="s">
         <v>163</v>
       </c>
+      <c r="E64" s="2">
+        <v>46230</v>
+      </c>
       <c r="F64" t="s">
         <v>75</v>
       </c>
@@ -9074,6 +9264,9 @@
       <c r="D65" t="s">
         <v>163</v>
       </c>
+      <c r="E65" s="2">
+        <v>46230</v>
+      </c>
       <c r="F65" t="s">
         <v>75</v>
       </c>
@@ -9184,6 +9377,9 @@
       <c r="D66" t="s">
         <v>166</v>
       </c>
+      <c r="E66" s="2">
+        <v>46230</v>
+      </c>
       <c r="F66" t="s">
         <v>75</v>
       </c>
@@ -9294,6 +9490,9 @@
       <c r="D67" t="s">
         <v>166</v>
       </c>
+      <c r="E67" s="2">
+        <v>46230</v>
+      </c>
       <c r="F67" t="s">
         <v>75</v>
       </c>
@@ -9404,6 +9603,9 @@
       <c r="D68" t="s">
         <v>169</v>
       </c>
+      <c r="E68" s="2">
+        <v>46230</v>
+      </c>
       <c r="F68" t="s">
         <v>75</v>
       </c>
@@ -9517,6 +9719,9 @@
       <c r="D69" t="s">
         <v>169</v>
       </c>
+      <c r="E69" s="2">
+        <v>46230</v>
+      </c>
       <c r="F69" t="s">
         <v>75</v>
       </c>
@@ -9627,6 +9832,9 @@
       <c r="D70" t="s">
         <v>172</v>
       </c>
+      <c r="E70" s="2">
+        <v>46230</v>
+      </c>
       <c r="F70" t="s">
         <v>75</v>
       </c>
@@ -9740,6 +9948,9 @@
       <c r="D71" t="s">
         <v>172</v>
       </c>
+      <c r="E71" s="2">
+        <v>46230</v>
+      </c>
       <c r="F71" t="s">
         <v>75</v>
       </c>
@@ -9850,6 +10061,9 @@
       <c r="D72" t="s">
         <v>175</v>
       </c>
+      <c r="E72" s="2">
+        <v>46230</v>
+      </c>
       <c r="F72" t="s">
         <v>75</v>
       </c>
@@ -9960,6 +10174,9 @@
       <c r="D73" t="s">
         <v>175</v>
       </c>
+      <c r="E73" s="2">
+        <v>46230</v>
+      </c>
       <c r="F73" t="s">
         <v>75</v>
       </c>
@@ -10070,6 +10287,9 @@
       <c r="D74" t="s">
         <v>178</v>
       </c>
+      <c r="E74" s="2">
+        <v>46230</v>
+      </c>
       <c r="F74" t="s">
         <v>75</v>
       </c>
@@ -10180,6 +10400,9 @@
       <c r="D75" t="s">
         <v>178</v>
       </c>
+      <c r="E75" s="2">
+        <v>46230</v>
+      </c>
       <c r="F75" t="s">
         <v>75</v>
       </c>
@@ -10290,6 +10513,9 @@
       <c r="D76" t="s">
         <v>181</v>
       </c>
+      <c r="E76" s="2">
+        <v>46230</v>
+      </c>
       <c r="F76" t="s">
         <v>75</v>
       </c>
@@ -10403,6 +10629,9 @@
       <c r="D77" t="s">
         <v>181</v>
       </c>
+      <c r="E77" s="2">
+        <v>46230</v>
+      </c>
       <c r="F77" t="s">
         <v>75</v>
       </c>
@@ -10513,6 +10742,9 @@
       <c r="D78" t="s">
         <v>184</v>
       </c>
+      <c r="E78" s="2">
+        <v>46230</v>
+      </c>
       <c r="F78" t="s">
         <v>75</v>
       </c>
@@ -10626,6 +10858,9 @@
       <c r="D79" t="s">
         <v>184</v>
       </c>
+      <c r="E79" s="2">
+        <v>46230</v>
+      </c>
       <c r="F79" t="s">
         <v>75</v>
       </c>
@@ -10736,6 +10971,9 @@
       <c r="D80" t="s">
         <v>187</v>
       </c>
+      <c r="E80" s="2">
+        <v>46230</v>
+      </c>
       <c r="F80" t="s">
         <v>62</v>
       </c>
@@ -10849,6 +11087,9 @@
       <c r="D81" t="s">
         <v>187</v>
       </c>
+      <c r="E81" s="2">
+        <v>46230</v>
+      </c>
       <c r="F81" t="s">
         <v>62</v>
       </c>
@@ -10962,6 +11203,9 @@
       <c r="D82" t="s">
         <v>190</v>
       </c>
+      <c r="E82" s="2">
+        <v>46230</v>
+      </c>
       <c r="F82" t="s">
         <v>62</v>
       </c>
@@ -11075,6 +11319,9 @@
       <c r="D83" t="s">
         <v>190</v>
       </c>
+      <c r="E83" s="2">
+        <v>46230</v>
+      </c>
       <c r="F83" t="s">
         <v>62</v>
       </c>
@@ -11185,6 +11432,9 @@
       <c r="D84" t="s">
         <v>193</v>
       </c>
+      <c r="E84" s="2">
+        <v>46230</v>
+      </c>
       <c r="F84" t="s">
         <v>62</v>
       </c>
@@ -11295,6 +11545,9 @@
       <c r="D85" t="s">
         <v>193</v>
       </c>
+      <c r="E85" s="2">
+        <v>46230</v>
+      </c>
       <c r="F85" t="s">
         <v>62</v>
       </c>
@@ -11405,6 +11658,9 @@
       <c r="D86" t="s">
         <v>196</v>
       </c>
+      <c r="E86" s="2">
+        <v>46230</v>
+      </c>
       <c r="F86" t="s">
         <v>62</v>
       </c>
@@ -11515,6 +11771,9 @@
       <c r="D87" t="s">
         <v>196</v>
       </c>
+      <c r="E87" s="2">
+        <v>46230</v>
+      </c>
       <c r="F87" t="s">
         <v>62</v>
       </c>
@@ -11625,6 +11884,9 @@
       <c r="D88" t="s">
         <v>199</v>
       </c>
+      <c r="E88" s="2">
+        <v>46230</v>
+      </c>
       <c r="F88" t="s">
         <v>62</v>
       </c>
@@ -11735,6 +11997,9 @@
       <c r="D89" t="s">
         <v>199</v>
       </c>
+      <c r="E89" s="2">
+        <v>46230</v>
+      </c>
       <c r="F89" t="s">
         <v>62</v>
       </c>
@@ -11845,6 +12110,9 @@
       <c r="D90" t="s">
         <v>202</v>
       </c>
+      <c r="E90" s="2">
+        <v>46230</v>
+      </c>
       <c r="F90" t="s">
         <v>62</v>
       </c>
@@ -11955,6 +12223,9 @@
       <c r="D91" t="s">
         <v>202</v>
       </c>
+      <c r="E91" s="2">
+        <v>46230</v>
+      </c>
       <c r="F91" t="s">
         <v>62</v>
       </c>
@@ -12065,6 +12336,9 @@
       <c r="D92" t="s">
         <v>205</v>
       </c>
+      <c r="E92" s="2">
+        <v>46230</v>
+      </c>
       <c r="F92" t="s">
         <v>62</v>
       </c>
@@ -12178,6 +12452,9 @@
       <c r="D93" t="s">
         <v>205</v>
       </c>
+      <c r="E93" s="2">
+        <v>46230</v>
+      </c>
       <c r="F93" t="s">
         <v>62</v>
       </c>
@@ -12288,6 +12565,9 @@
       <c r="D94" t="s">
         <v>208</v>
       </c>
+      <c r="E94" s="2">
+        <v>46230</v>
+      </c>
       <c r="F94" t="s">
         <v>62</v>
       </c>
@@ -12398,6 +12678,9 @@
       <c r="D95" t="s">
         <v>208</v>
       </c>
+      <c r="E95" s="2">
+        <v>46230</v>
+      </c>
       <c r="F95" t="s">
         <v>62</v>
       </c>
@@ -12508,6 +12791,9 @@
       <c r="D96" t="s">
         <v>211</v>
       </c>
+      <c r="E96" s="2">
+        <v>46230</v>
+      </c>
       <c r="F96" t="s">
         <v>62</v>
       </c>
@@ -12621,6 +12907,9 @@
       <c r="D97" t="s">
         <v>211</v>
       </c>
+      <c r="E97" s="2">
+        <v>46230</v>
+      </c>
       <c r="F97" t="s">
         <v>62</v>
       </c>
@@ -12731,6 +13020,9 @@
       <c r="D98" t="s">
         <v>214</v>
       </c>
+      <c r="E98" s="2">
+        <v>46230</v>
+      </c>
       <c r="F98" t="s">
         <v>62</v>
       </c>
@@ -12844,6 +13136,9 @@
       <c r="D99" t="s">
         <v>214</v>
       </c>
+      <c r="E99" s="2">
+        <v>46230</v>
+      </c>
       <c r="F99" t="s">
         <v>62</v>
       </c>
@@ -12957,6 +13252,9 @@
       <c r="D100" t="s">
         <v>217</v>
       </c>
+      <c r="E100" s="2">
+        <v>46230</v>
+      </c>
       <c r="F100" t="s">
         <v>62</v>
       </c>
@@ -13070,6 +13368,9 @@
       <c r="D101" t="s">
         <v>217</v>
       </c>
+      <c r="E101" s="2">
+        <v>46230</v>
+      </c>
       <c r="F101" t="s">
         <v>62</v>
       </c>
@@ -13180,6 +13481,9 @@
       <c r="D102" t="s">
         <v>220</v>
       </c>
+      <c r="E102" s="2">
+        <v>46230</v>
+      </c>
       <c r="F102" t="s">
         <v>62</v>
       </c>
@@ -13290,6 +13594,9 @@
       <c r="D103" t="s">
         <v>220</v>
       </c>
+      <c r="E103" s="2">
+        <v>46230</v>
+      </c>
       <c r="F103" t="s">
         <v>62</v>
       </c>
@@ -13400,6 +13707,9 @@
       <c r="D104" t="s">
         <v>223</v>
       </c>
+      <c r="E104" s="2">
+        <v>46230</v>
+      </c>
       <c r="F104" t="s">
         <v>62</v>
       </c>
@@ -13510,6 +13820,9 @@
       <c r="D105" t="s">
         <v>223</v>
       </c>
+      <c r="E105" s="2">
+        <v>46230</v>
+      </c>
       <c r="F105" t="s">
         <v>62</v>
       </c>
@@ -13620,6 +13933,9 @@
       <c r="D106" t="s">
         <v>226</v>
       </c>
+      <c r="E106" s="2">
+        <v>46230</v>
+      </c>
       <c r="F106" t="s">
         <v>62</v>
       </c>
@@ -13730,6 +14046,9 @@
       <c r="D107" t="s">
         <v>226</v>
       </c>
+      <c r="E107" s="2">
+        <v>46230</v>
+      </c>
       <c r="F107" t="s">
         <v>62</v>
       </c>
@@ -13840,6 +14159,9 @@
       <c r="D108" t="s">
         <v>229</v>
       </c>
+      <c r="E108" s="2">
+        <v>46230</v>
+      </c>
       <c r="F108" t="s">
         <v>62</v>
       </c>
@@ -13953,6 +14275,9 @@
       <c r="D109" t="s">
         <v>229</v>
       </c>
+      <c r="E109" s="2">
+        <v>46230</v>
+      </c>
       <c r="F109" t="s">
         <v>62</v>
       </c>
@@ -14063,6 +14388,9 @@
       <c r="D110" t="s">
         <v>232</v>
       </c>
+      <c r="E110" s="2">
+        <v>46230</v>
+      </c>
       <c r="F110" t="s">
         <v>62</v>
       </c>
@@ -14176,6 +14504,9 @@
       <c r="D111" t="s">
         <v>232</v>
       </c>
+      <c r="E111" s="2">
+        <v>46230</v>
+      </c>
       <c r="F111" t="s">
         <v>62</v>
       </c>
@@ -14286,6 +14617,9 @@
       <c r="D112" t="s">
         <v>235</v>
       </c>
+      <c r="E112" s="2">
+        <v>46230</v>
+      </c>
       <c r="F112" t="s">
         <v>62</v>
       </c>
@@ -14396,6 +14730,9 @@
       <c r="D113" t="s">
         <v>235</v>
       </c>
+      <c r="E113" s="2">
+        <v>46230</v>
+      </c>
       <c r="F113" t="s">
         <v>62</v>
       </c>
@@ -14506,6 +14843,9 @@
       <c r="D114" t="s">
         <v>238</v>
       </c>
+      <c r="E114" s="2">
+        <v>46230</v>
+      </c>
       <c r="F114" t="s">
         <v>62</v>
       </c>
@@ -14616,6 +14956,9 @@
       <c r="D115" t="s">
         <v>238</v>
       </c>
+      <c r="E115" s="2">
+        <v>46230</v>
+      </c>
       <c r="F115" t="s">
         <v>62</v>
       </c>
@@ -14726,6 +15069,9 @@
       <c r="D116" t="s">
         <v>241</v>
       </c>
+      <c r="E116" s="2">
+        <v>46230</v>
+      </c>
       <c r="F116" t="s">
         <v>62</v>
       </c>
@@ -14836,6 +15182,9 @@
       <c r="D117" t="s">
         <v>241</v>
       </c>
+      <c r="E117" s="2">
+        <v>46230</v>
+      </c>
       <c r="F117" t="s">
         <v>62</v>
       </c>
@@ -14946,6 +15295,9 @@
       <c r="D118" t="s">
         <v>244</v>
       </c>
+      <c r="E118" s="2">
+        <v>46230</v>
+      </c>
       <c r="F118" t="s">
         <v>62</v>
       </c>
@@ -15056,6 +15408,9 @@
       <c r="D119" t="s">
         <v>244</v>
       </c>
+      <c r="E119" s="2">
+        <v>46230</v>
+      </c>
       <c r="F119" t="s">
         <v>62</v>
       </c>
@@ -15166,6 +15521,9 @@
       <c r="D120" t="s">
         <v>247</v>
       </c>
+      <c r="E120" s="2">
+        <v>46230</v>
+      </c>
       <c r="F120" t="s">
         <v>62</v>
       </c>
@@ -15276,6 +15634,9 @@
       <c r="D121" t="s">
         <v>247</v>
       </c>
+      <c r="E121" s="2">
+        <v>46230</v>
+      </c>
       <c r="F121" t="s">
         <v>62</v>
       </c>
@@ -15386,6 +15747,9 @@
       <c r="D122" t="s">
         <v>250</v>
       </c>
+      <c r="E122" s="2">
+        <v>46230</v>
+      </c>
       <c r="F122" t="s">
         <v>62</v>
       </c>
@@ -15499,6 +15863,9 @@
       <c r="D123" t="s">
         <v>250</v>
       </c>
+      <c r="E123" s="2">
+        <v>46230</v>
+      </c>
       <c r="F123" t="s">
         <v>62</v>
       </c>
@@ -15609,6 +15976,9 @@
       <c r="D124" t="s">
         <v>253</v>
       </c>
+      <c r="E124" s="2">
+        <v>46230</v>
+      </c>
       <c r="F124" t="s">
         <v>62</v>
       </c>
@@ -15722,6 +16092,9 @@
       <c r="D125" t="s">
         <v>253</v>
       </c>
+      <c r="E125" s="2">
+        <v>46230</v>
+      </c>
       <c r="F125" t="s">
         <v>62</v>
       </c>
@@ -15832,6 +16205,9 @@
       <c r="D126" t="s">
         <v>256</v>
       </c>
+      <c r="E126" s="2">
+        <v>46230</v>
+      </c>
       <c r="F126" t="s">
         <v>75</v>
       </c>
@@ -15945,6 +16321,9 @@
       <c r="D127" t="s">
         <v>256</v>
       </c>
+      <c r="E127" s="2">
+        <v>46230</v>
+      </c>
       <c r="F127" t="s">
         <v>75</v>
       </c>
@@ -16055,6 +16434,9 @@
       <c r="D128" t="s">
         <v>259</v>
       </c>
+      <c r="E128" s="2">
+        <v>46230</v>
+      </c>
       <c r="F128" t="s">
         <v>75</v>
       </c>
@@ -16165,6 +16547,9 @@
       <c r="D129" t="s">
         <v>259</v>
       </c>
+      <c r="E129" s="2">
+        <v>46230</v>
+      </c>
       <c r="F129" t="s">
         <v>75</v>
       </c>
@@ -16275,6 +16660,9 @@
       <c r="D130" t="s">
         <v>262</v>
       </c>
+      <c r="E130" s="2">
+        <v>46230</v>
+      </c>
       <c r="F130" t="s">
         <v>75</v>
       </c>
@@ -16385,6 +16773,9 @@
       <c r="D131" t="s">
         <v>262</v>
       </c>
+      <c r="E131" s="2">
+        <v>46230</v>
+      </c>
       <c r="F131" t="s">
         <v>75</v>
       </c>
@@ -16495,6 +16886,9 @@
       <c r="D132" t="s">
         <v>265</v>
       </c>
+      <c r="E132" s="2">
+        <v>46230</v>
+      </c>
       <c r="F132" t="s">
         <v>75</v>
       </c>
@@ -16608,6 +17002,9 @@
       <c r="D133" t="s">
         <v>265</v>
       </c>
+      <c r="E133" s="2">
+        <v>46230</v>
+      </c>
       <c r="F133" t="s">
         <v>75</v>
       </c>
@@ -16718,6 +17115,9 @@
       <c r="D134" t="s">
         <v>268</v>
       </c>
+      <c r="E134" s="2">
+        <v>46230</v>
+      </c>
       <c r="F134" t="s">
         <v>75</v>
       </c>
@@ -16831,6 +17231,9 @@
       <c r="D135" t="s">
         <v>268</v>
       </c>
+      <c r="E135" s="2">
+        <v>46230</v>
+      </c>
       <c r="F135" t="s">
         <v>75</v>
       </c>
@@ -16941,6 +17344,9 @@
       <c r="D136" t="s">
         <v>271</v>
       </c>
+      <c r="E136" s="2">
+        <v>46230</v>
+      </c>
       <c r="F136" t="s">
         <v>75</v>
       </c>
@@ -17051,6 +17457,9 @@
       <c r="D137" t="s">
         <v>271</v>
       </c>
+      <c r="E137" s="2">
+        <v>46230</v>
+      </c>
       <c r="F137" t="s">
         <v>75</v>
       </c>
@@ -17161,6 +17570,9 @@
       <c r="D138" t="s">
         <v>274</v>
       </c>
+      <c r="E138" s="2">
+        <v>46230</v>
+      </c>
       <c r="F138" t="s">
         <v>75</v>
       </c>
@@ -17273,6 +17685,9 @@
       </c>
       <c r="D139" t="s">
         <v>274</v>
+      </c>
+      <c r="E139" s="2">
+        <v>46230</v>
       </c>
       <c r="F139" t="s">
         <v>75</v>
@@ -17384,6 +17799,9 @@
       <c r="D140" t="s">
         <v>277</v>
       </c>
+      <c r="E140" s="2">
+        <v>46230</v>
+      </c>
       <c r="F140" t="s">
         <v>75</v>
       </c>
@@ -17494,6 +17912,9 @@
       <c r="D141" t="s">
         <v>277</v>
       </c>
+      <c r="E141" s="2">
+        <v>46230</v>
+      </c>
       <c r="F141" t="s">
         <v>75</v>
       </c>
@@ -17604,6 +18025,9 @@
       <c r="D142" t="s">
         <v>280</v>
       </c>
+      <c r="E142" s="2">
+        <v>46230</v>
+      </c>
       <c r="F142" t="s">
         <v>75</v>
       </c>
@@ -17714,6 +18138,9 @@
       <c r="D143" t="s">
         <v>280</v>
       </c>
+      <c r="E143" s="2">
+        <v>46230</v>
+      </c>
       <c r="F143" t="s">
         <v>75</v>
       </c>
@@ -17824,6 +18251,9 @@
       <c r="D144" t="s">
         <v>283</v>
       </c>
+      <c r="E144" s="2">
+        <v>46230</v>
+      </c>
       <c r="F144" t="s">
         <v>75</v>
       </c>
@@ -17934,6 +18364,9 @@
       <c r="D145" t="s">
         <v>283</v>
       </c>
+      <c r="E145" s="2">
+        <v>46230</v>
+      </c>
       <c r="F145" t="s">
         <v>75</v>
       </c>
@@ -18044,6 +18477,9 @@
       <c r="D146" t="s">
         <v>286</v>
       </c>
+      <c r="E146" s="2">
+        <v>46230</v>
+      </c>
       <c r="F146" t="s">
         <v>62</v>
       </c>
@@ -18157,6 +18593,9 @@
       <c r="D147" t="s">
         <v>286</v>
       </c>
+      <c r="E147" s="2">
+        <v>46230</v>
+      </c>
       <c r="F147" t="s">
         <v>62</v>
       </c>
@@ -18270,6 +18709,9 @@
       <c r="D148" t="s">
         <v>289</v>
       </c>
+      <c r="E148" s="2">
+        <v>46230</v>
+      </c>
       <c r="F148" t="s">
         <v>62</v>
       </c>
@@ -18383,6 +18825,9 @@
       <c r="D149" t="s">
         <v>289</v>
       </c>
+      <c r="E149" s="2">
+        <v>46230</v>
+      </c>
       <c r="F149" t="s">
         <v>62</v>
       </c>
@@ -18493,6 +18938,9 @@
       <c r="D150" t="s">
         <v>292</v>
       </c>
+      <c r="E150" s="2">
+        <v>46230</v>
+      </c>
       <c r="F150" t="s">
         <v>62</v>
       </c>
@@ -18606,6 +19054,9 @@
       <c r="D151" t="s">
         <v>292</v>
       </c>
+      <c r="E151" s="2">
+        <v>46230</v>
+      </c>
       <c r="F151" t="s">
         <v>62</v>
       </c>
@@ -18719,6 +19170,9 @@
       <c r="D152" t="s">
         <v>295</v>
       </c>
+      <c r="E152" s="2">
+        <v>46230</v>
+      </c>
       <c r="F152" t="s">
         <v>62</v>
       </c>
@@ -18832,6 +19286,9 @@
       <c r="D153" t="s">
         <v>295</v>
       </c>
+      <c r="E153" s="2">
+        <v>46230</v>
+      </c>
       <c r="F153" t="s">
         <v>62</v>
       </c>
@@ -18942,6 +19399,9 @@
       <c r="D154" t="s">
         <v>298</v>
       </c>
+      <c r="E154" s="2">
+        <v>46230</v>
+      </c>
       <c r="F154" t="s">
         <v>62</v>
       </c>
@@ -19055,6 +19515,9 @@
       <c r="D155" t="s">
         <v>298</v>
       </c>
+      <c r="E155" s="2">
+        <v>46230</v>
+      </c>
       <c r="F155" t="s">
         <v>62</v>
       </c>
@@ -19165,6 +19628,9 @@
       <c r="D156" t="s">
         <v>301</v>
       </c>
+      <c r="E156" s="2">
+        <v>46230</v>
+      </c>
       <c r="F156" t="s">
         <v>62</v>
       </c>
@@ -19275,6 +19741,9 @@
       <c r="D157" t="s">
         <v>301</v>
       </c>
+      <c r="E157" s="2">
+        <v>46230</v>
+      </c>
       <c r="F157" t="s">
         <v>62</v>
       </c>
@@ -19385,6 +19854,9 @@
       <c r="D158" t="s">
         <v>304</v>
       </c>
+      <c r="E158" s="2">
+        <v>46230</v>
+      </c>
       <c r="F158" t="s">
         <v>62</v>
       </c>
@@ -19495,6 +19967,9 @@
       <c r="D159" t="s">
         <v>304</v>
       </c>
+      <c r="E159" s="2">
+        <v>46230</v>
+      </c>
       <c r="F159" t="s">
         <v>62</v>
       </c>
@@ -19605,6 +20080,9 @@
       <c r="D160" t="s">
         <v>307</v>
       </c>
+      <c r="E160" s="2">
+        <v>46230</v>
+      </c>
       <c r="F160" t="s">
         <v>62</v>
       </c>
@@ -19715,6 +20193,9 @@
       <c r="D161" t="s">
         <v>307</v>
       </c>
+      <c r="E161" s="2">
+        <v>46230</v>
+      </c>
       <c r="F161" t="s">
         <v>62</v>
       </c>
@@ -19825,6 +20306,9 @@
       <c r="D162" t="s">
         <v>310</v>
       </c>
+      <c r="E162" s="2">
+        <v>46230</v>
+      </c>
       <c r="F162" t="s">
         <v>62</v>
       </c>
@@ -19938,6 +20422,9 @@
       <c r="D163" t="s">
         <v>310</v>
       </c>
+      <c r="E163" s="2">
+        <v>46230</v>
+      </c>
       <c r="F163" t="s">
         <v>62</v>
       </c>
@@ -20048,6 +20535,9 @@
       <c r="D164" t="s">
         <v>313</v>
       </c>
+      <c r="E164" s="2">
+        <v>46230</v>
+      </c>
       <c r="F164" t="s">
         <v>62</v>
       </c>
@@ -20161,6 +20651,9 @@
       <c r="D165" t="s">
         <v>313</v>
       </c>
+      <c r="E165" s="2">
+        <v>46230</v>
+      </c>
       <c r="F165" t="s">
         <v>62</v>
       </c>
@@ -20274,6 +20767,9 @@
       <c r="D166" t="s">
         <v>316</v>
       </c>
+      <c r="E166" s="2">
+        <v>46230</v>
+      </c>
       <c r="F166" t="s">
         <v>317</v>
       </c>
@@ -20387,6 +20883,9 @@
       <c r="D167" t="s">
         <v>316</v>
       </c>
+      <c r="E167" s="2">
+        <v>46230</v>
+      </c>
       <c r="F167" t="s">
         <v>317</v>
       </c>
@@ -20500,6 +20999,9 @@
       <c r="D168" t="s">
         <v>322</v>
       </c>
+      <c r="E168" s="2">
+        <v>46230</v>
+      </c>
       <c r="F168" t="s">
         <v>317</v>
       </c>
@@ -20612,6 +21114,9 @@
       </c>
       <c r="D169" t="s">
         <v>322</v>
+      </c>
+      <c r="E169" s="2">
+        <v>46230</v>
       </c>
       <c r="F169" t="s">
         <v>317</v>
@@ -20723,6 +21228,9 @@
       <c r="D170" t="s">
         <v>325</v>
       </c>
+      <c r="E170" s="2">
+        <v>46230</v>
+      </c>
       <c r="F170" t="s">
         <v>317</v>
       </c>
@@ -20833,6 +21341,9 @@
       <c r="D171" t="s">
         <v>325</v>
       </c>
+      <c r="E171" s="2">
+        <v>46230</v>
+      </c>
       <c r="F171" t="s">
         <v>317</v>
       </c>
@@ -20943,6 +21454,9 @@
       <c r="D172" t="s">
         <v>325</v>
       </c>
+      <c r="E172" s="2">
+        <v>46230</v>
+      </c>
       <c r="F172" t="s">
         <v>317</v>
       </c>
@@ -21053,6 +21567,9 @@
       <c r="D173" t="s">
         <v>325</v>
       </c>
+      <c r="E173" s="2">
+        <v>46230</v>
+      </c>
       <c r="F173" t="s">
         <v>317</v>
       </c>
@@ -21163,6 +21680,9 @@
       <c r="D174" t="s">
         <v>330</v>
       </c>
+      <c r="E174" s="2">
+        <v>46230</v>
+      </c>
       <c r="F174" t="s">
         <v>317</v>
       </c>
@@ -21276,6 +21796,9 @@
       <c r="D175" t="s">
         <v>330</v>
       </c>
+      <c r="E175" s="2">
+        <v>46230</v>
+      </c>
       <c r="F175" t="s">
         <v>317</v>
       </c>
@@ -21386,6 +21909,9 @@
       <c r="D176" t="s">
         <v>333</v>
       </c>
+      <c r="E176" s="2">
+        <v>46230</v>
+      </c>
       <c r="F176" t="s">
         <v>317</v>
       </c>
@@ -21496,6 +22022,9 @@
       <c r="D177" t="s">
         <v>333</v>
       </c>
+      <c r="E177" s="2">
+        <v>46230</v>
+      </c>
       <c r="F177" t="s">
         <v>317</v>
       </c>
@@ -21606,6 +22135,9 @@
       <c r="D178" t="s">
         <v>330</v>
       </c>
+      <c r="E178" s="2">
+        <v>46230</v>
+      </c>
       <c r="F178" t="s">
         <v>317</v>
       </c>
@@ -21716,6 +22248,9 @@
       <c r="D179" t="s">
         <v>330</v>
       </c>
+      <c r="E179" s="2">
+        <v>46230</v>
+      </c>
       <c r="F179" t="s">
         <v>317</v>
       </c>
@@ -21826,6 +22361,9 @@
       <c r="D180" t="s">
         <v>338</v>
       </c>
+      <c r="E180" s="2">
+        <v>46230</v>
+      </c>
       <c r="F180" t="s">
         <v>317</v>
       </c>
@@ -21936,6 +22474,9 @@
       <c r="D181" t="s">
         <v>338</v>
       </c>
+      <c r="E181" s="2">
+        <v>46230</v>
+      </c>
       <c r="F181" t="s">
         <v>317</v>
       </c>
@@ -22046,6 +22587,9 @@
       <c r="D182" t="s">
         <v>341</v>
       </c>
+      <c r="E182" s="2">
+        <v>46230</v>
+      </c>
       <c r="F182" t="s">
         <v>317</v>
       </c>
@@ -22159,6 +22703,9 @@
       <c r="D183" t="s">
         <v>341</v>
       </c>
+      <c r="E183" s="2">
+        <v>46230</v>
+      </c>
       <c r="F183" t="s">
         <v>317</v>
       </c>
@@ -22269,6 +22816,9 @@
       <c r="D184" t="s">
         <v>344</v>
       </c>
+      <c r="E184" s="2">
+        <v>46230</v>
+      </c>
       <c r="F184" t="s">
         <v>317</v>
       </c>
@@ -22382,6 +22932,9 @@
       <c r="D185" t="s">
         <v>344</v>
       </c>
+      <c r="E185" s="2">
+        <v>46230</v>
+      </c>
       <c r="F185" t="s">
         <v>317</v>
       </c>
@@ -22492,6 +23045,9 @@
       <c r="D186" t="s">
         <v>344</v>
       </c>
+      <c r="E186" s="2">
+        <v>46230</v>
+      </c>
       <c r="F186" t="s">
         <v>317</v>
       </c>
@@ -22602,6 +23158,9 @@
       <c r="D187" t="s">
         <v>344</v>
       </c>
+      <c r="E187" s="2">
+        <v>46230</v>
+      </c>
       <c r="F187" t="s">
         <v>317</v>
       </c>
@@ -22712,6 +23271,9 @@
       <c r="D188" t="s">
         <v>349</v>
       </c>
+      <c r="E188" s="2">
+        <v>46230</v>
+      </c>
       <c r="F188" t="s">
         <v>317</v>
       </c>
@@ -22822,6 +23384,9 @@
       <c r="D189" t="s">
         <v>349</v>
       </c>
+      <c r="E189" s="2">
+        <v>46230</v>
+      </c>
       <c r="F189" t="s">
         <v>317</v>
       </c>
@@ -22932,6 +23497,9 @@
       <c r="D190" t="s">
         <v>352</v>
       </c>
+      <c r="E190" s="2">
+        <v>46230</v>
+      </c>
       <c r="F190" t="s">
         <v>317</v>
       </c>
@@ -23045,6 +23613,9 @@
       <c r="D191" t="s">
         <v>352</v>
       </c>
+      <c r="E191" s="2">
+        <v>46230</v>
+      </c>
       <c r="F191" t="s">
         <v>317</v>
       </c>
@@ -23155,6 +23726,9 @@
       <c r="D192" t="s">
         <v>352</v>
       </c>
+      <c r="E192" s="2">
+        <v>46230</v>
+      </c>
       <c r="F192" t="s">
         <v>317</v>
       </c>
@@ -23265,6 +23839,9 @@
       <c r="D193" t="s">
         <v>352</v>
       </c>
+      <c r="E193" s="2">
+        <v>46230</v>
+      </c>
       <c r="F193" t="s">
         <v>317</v>
       </c>
@@ -23375,6 +23952,9 @@
       <c r="D194" t="s">
         <v>352</v>
       </c>
+      <c r="E194" s="2">
+        <v>46230</v>
+      </c>
       <c r="F194" t="s">
         <v>317</v>
       </c>
@@ -23485,6 +24065,9 @@
       <c r="D195" t="s">
         <v>352</v>
       </c>
+      <c r="E195" s="2">
+        <v>46230</v>
+      </c>
       <c r="F195" t="s">
         <v>317</v>
       </c>
@@ -23595,6 +24178,9 @@
       <c r="D196" t="s">
         <v>359</v>
       </c>
+      <c r="E196" s="2">
+        <v>46230</v>
+      </c>
       <c r="F196" t="s">
         <v>317</v>
       </c>
@@ -23705,6 +24291,9 @@
       <c r="D197" t="s">
         <v>359</v>
       </c>
+      <c r="E197" s="2">
+        <v>46230</v>
+      </c>
       <c r="F197" t="s">
         <v>317</v>
       </c>
@@ -23815,6 +24404,9 @@
       <c r="D198" t="s">
         <v>362</v>
       </c>
+      <c r="E198" s="2">
+        <v>46230</v>
+      </c>
       <c r="F198" t="s">
         <v>317</v>
       </c>
@@ -23925,6 +24517,9 @@
       <c r="D199" t="s">
         <v>362</v>
       </c>
+      <c r="E199" s="2">
+        <v>46230</v>
+      </c>
       <c r="F199" t="s">
         <v>317</v>
       </c>
@@ -24035,6 +24630,9 @@
       <c r="D200" t="s">
         <v>362</v>
       </c>
+      <c r="E200" s="2">
+        <v>46230</v>
+      </c>
       <c r="F200" t="s">
         <v>317</v>
       </c>
@@ -24148,6 +24746,9 @@
       <c r="D201" t="s">
         <v>362</v>
       </c>
+      <c r="E201" s="2">
+        <v>46230</v>
+      </c>
       <c r="F201" t="s">
         <v>317</v>
       </c>
@@ -24258,6 +24859,9 @@
       <c r="D202" t="s">
         <v>362</v>
       </c>
+      <c r="E202" s="2">
+        <v>46230</v>
+      </c>
       <c r="F202" t="s">
         <v>317</v>
       </c>
@@ -24368,6 +24972,9 @@
       <c r="D203" t="s">
         <v>362</v>
       </c>
+      <c r="E203" s="2">
+        <v>46230</v>
+      </c>
       <c r="F203" t="s">
         <v>317</v>
       </c>
@@ -24478,6 +25085,9 @@
       <c r="D204" t="s">
         <v>369</v>
       </c>
+      <c r="E204" s="2">
+        <v>46230</v>
+      </c>
       <c r="F204" t="s">
         <v>317</v>
       </c>
@@ -24588,6 +25198,9 @@
       <c r="D205" t="s">
         <v>369</v>
       </c>
+      <c r="E205" s="2">
+        <v>46230</v>
+      </c>
       <c r="F205" t="s">
         <v>317</v>
       </c>
@@ -24698,6 +25311,9 @@
       <c r="D206" t="s">
         <v>369</v>
       </c>
+      <c r="E206" s="2">
+        <v>46230</v>
+      </c>
       <c r="F206" t="s">
         <v>317</v>
       </c>
@@ -24808,6 +25424,9 @@
       <c r="D207" t="s">
         <v>369</v>
       </c>
+      <c r="E207" s="2">
+        <v>46230</v>
+      </c>
       <c r="F207" t="s">
         <v>317</v>
       </c>
@@ -24918,6 +25537,9 @@
       <c r="D208" t="s">
         <v>369</v>
       </c>
+      <c r="E208" s="2">
+        <v>46230</v>
+      </c>
       <c r="F208" t="s">
         <v>317</v>
       </c>
@@ -25031,6 +25653,9 @@
       <c r="D209" t="s">
         <v>369</v>
       </c>
+      <c r="E209" s="2">
+        <v>46230</v>
+      </c>
       <c r="F209" t="s">
         <v>317</v>
       </c>
@@ -25141,6 +25766,9 @@
       <c r="D210" t="s">
         <v>376</v>
       </c>
+      <c r="E210" s="2">
+        <v>46230</v>
+      </c>
       <c r="F210" t="s">
         <v>317</v>
       </c>
@@ -25254,6 +25882,9 @@
       <c r="D211" t="s">
         <v>376</v>
       </c>
+      <c r="E211" s="2">
+        <v>46230</v>
+      </c>
       <c r="F211" t="s">
         <v>317</v>
       </c>
@@ -25364,6 +25995,9 @@
       <c r="D212" t="s">
         <v>379</v>
       </c>
+      <c r="E212" s="2">
+        <v>46230</v>
+      </c>
       <c r="F212" t="s">
         <v>317</v>
       </c>
@@ -25474,6 +26108,9 @@
       <c r="D213" t="s">
         <v>379</v>
       </c>
+      <c r="E213" s="2">
+        <v>46230</v>
+      </c>
       <c r="F213" t="s">
         <v>317</v>
       </c>
@@ -25584,6 +26221,9 @@
       <c r="D214" t="s">
         <v>376</v>
       </c>
+      <c r="E214" s="2">
+        <v>46230</v>
+      </c>
       <c r="F214" t="s">
         <v>317</v>
       </c>
@@ -25697,6 +26337,9 @@
       <c r="D215" t="s">
         <v>376</v>
       </c>
+      <c r="E215" s="2">
+        <v>46230</v>
+      </c>
       <c r="F215" t="s">
         <v>317</v>
       </c>
@@ -25807,6 +26450,9 @@
       <c r="D216" t="s">
         <v>376</v>
       </c>
+      <c r="E216" s="2">
+        <v>46230</v>
+      </c>
       <c r="F216" t="s">
         <v>317</v>
       </c>
@@ -25920,6 +26566,9 @@
       <c r="D217" t="s">
         <v>376</v>
       </c>
+      <c r="E217" s="2">
+        <v>46230</v>
+      </c>
       <c r="F217" t="s">
         <v>317</v>
       </c>
@@ -26030,6 +26679,9 @@
       <c r="D218" t="s">
         <v>379</v>
       </c>
+      <c r="E218" s="2">
+        <v>46230</v>
+      </c>
       <c r="F218" t="s">
         <v>317</v>
       </c>
@@ -26140,6 +26792,9 @@
       <c r="D219" t="s">
         <v>379</v>
       </c>
+      <c r="E219" s="2">
+        <v>46230</v>
+      </c>
       <c r="F219" t="s">
         <v>317</v>
       </c>
@@ -26250,6 +26905,9 @@
       <c r="D220" t="s">
         <v>379</v>
       </c>
+      <c r="E220" s="2">
+        <v>46230</v>
+      </c>
       <c r="F220" t="s">
         <v>317</v>
       </c>
@@ -26363,6 +27021,9 @@
       <c r="D221" t="s">
         <v>379</v>
       </c>
+      <c r="E221" s="2">
+        <v>46230</v>
+      </c>
       <c r="F221" t="s">
         <v>317</v>
       </c>
@@ -26473,6 +27134,9 @@
       <c r="D222" t="s">
         <v>390</v>
       </c>
+      <c r="E222" s="2">
+        <v>46230</v>
+      </c>
       <c r="F222" t="s">
         <v>317</v>
       </c>
@@ -26586,6 +27250,9 @@
       <c r="D223" t="s">
         <v>390</v>
       </c>
+      <c r="E223" s="2">
+        <v>46230</v>
+      </c>
       <c r="F223" t="s">
         <v>317</v>
       </c>
@@ -26699,6 +27366,9 @@
       <c r="D224" t="s">
         <v>393</v>
       </c>
+      <c r="E224" s="2">
+        <v>46230</v>
+      </c>
       <c r="F224" t="s">
         <v>317</v>
       </c>
@@ -26812,6 +27482,9 @@
       <c r="D225" t="s">
         <v>393</v>
       </c>
+      <c r="E225" s="2">
+        <v>46230</v>
+      </c>
       <c r="F225" t="s">
         <v>317</v>
       </c>
@@ -26922,6 +27595,9 @@
       <c r="D226" t="s">
         <v>396</v>
       </c>
+      <c r="E226" s="2">
+        <v>46230</v>
+      </c>
       <c r="F226" t="s">
         <v>317</v>
       </c>
@@ -27032,6 +27708,9 @@
       <c r="D227" t="s">
         <v>396</v>
       </c>
+      <c r="E227" s="2">
+        <v>46230</v>
+      </c>
       <c r="F227" t="s">
         <v>317</v>
       </c>
@@ -27142,6 +27821,9 @@
       <c r="D228" t="s">
         <v>399</v>
       </c>
+      <c r="E228" s="2">
+        <v>46230</v>
+      </c>
       <c r="F228" t="s">
         <v>317</v>
       </c>
@@ -27255,6 +27937,9 @@
       <c r="D229" t="s">
         <v>399</v>
       </c>
+      <c r="E229" s="2">
+        <v>46230</v>
+      </c>
       <c r="F229" t="s">
         <v>317</v>
       </c>
@@ -27368,6 +28053,9 @@
       <c r="D230" t="s">
         <v>401</v>
       </c>
+      <c r="E230" s="2">
+        <v>46230</v>
+      </c>
       <c r="F230" t="s">
         <v>317</v>
       </c>
@@ -27481,6 +28169,9 @@
       <c r="D231" t="s">
         <v>401</v>
       </c>
+      <c r="E231" s="2">
+        <v>46230</v>
+      </c>
       <c r="F231" t="s">
         <v>317</v>
       </c>
@@ -27591,6 +28282,9 @@
       <c r="D232" t="s">
         <v>404</v>
       </c>
+      <c r="E232" s="2">
+        <v>46230</v>
+      </c>
       <c r="F232" t="s">
         <v>317</v>
       </c>
@@ -27701,6 +28395,9 @@
       <c r="D233" t="s">
         <v>404</v>
       </c>
+      <c r="E233" s="2">
+        <v>46230</v>
+      </c>
       <c r="F233" t="s">
         <v>317</v>
       </c>
@@ -27811,6 +28508,9 @@
       <c r="D234" t="s">
         <v>407</v>
       </c>
+      <c r="E234" s="2">
+        <v>46230</v>
+      </c>
       <c r="F234" t="s">
         <v>317</v>
       </c>
@@ -27921,6 +28621,9 @@
       <c r="D235" t="s">
         <v>407</v>
       </c>
+      <c r="E235" s="2">
+        <v>46230</v>
+      </c>
       <c r="F235" t="s">
         <v>317</v>
       </c>
@@ -28031,6 +28734,9 @@
       <c r="D236" t="s">
         <v>410</v>
       </c>
+      <c r="E236" s="2">
+        <v>46230</v>
+      </c>
       <c r="F236" t="s">
         <v>317</v>
       </c>
@@ -28144,6 +28850,9 @@
       <c r="D237" t="s">
         <v>410</v>
       </c>
+      <c r="E237" s="2">
+        <v>46230</v>
+      </c>
       <c r="F237" t="s">
         <v>317</v>
       </c>
@@ -28254,6 +28963,9 @@
       <c r="D238" t="s">
         <v>413</v>
       </c>
+      <c r="E238" s="2">
+        <v>46230</v>
+      </c>
       <c r="F238" t="s">
         <v>317</v>
       </c>
@@ -28367,6 +29079,9 @@
       <c r="D239" t="s">
         <v>413</v>
       </c>
+      <c r="E239" s="2">
+        <v>46230</v>
+      </c>
       <c r="F239" t="s">
         <v>317</v>
       </c>
@@ -28477,6 +29192,9 @@
       <c r="D240" t="s">
         <v>416</v>
       </c>
+      <c r="E240" s="2">
+        <v>46230</v>
+      </c>
       <c r="F240" t="s">
         <v>317</v>
       </c>
@@ -28587,6 +29305,9 @@
       <c r="D241" t="s">
         <v>416</v>
       </c>
+      <c r="E241" s="2">
+        <v>46230</v>
+      </c>
       <c r="F241" t="s">
         <v>317</v>
       </c>
@@ -28697,6 +29418,9 @@
       <c r="D242" t="s">
         <v>419</v>
       </c>
+      <c r="E242" s="2">
+        <v>46230</v>
+      </c>
       <c r="F242" t="s">
         <v>317</v>
       </c>
@@ -28807,6 +29531,9 @@
       <c r="D243" t="s">
         <v>419</v>
       </c>
+      <c r="E243" s="2">
+        <v>46230</v>
+      </c>
       <c r="F243" t="s">
         <v>317</v>
       </c>
@@ -28917,6 +29644,9 @@
       <c r="D244" t="s">
         <v>422</v>
       </c>
+      <c r="E244" s="2">
+        <v>46230</v>
+      </c>
       <c r="F244" t="s">
         <v>317</v>
       </c>
@@ -29027,6 +29757,9 @@
       <c r="D245" t="s">
         <v>422</v>
       </c>
+      <c r="E245" s="2">
+        <v>46230</v>
+      </c>
       <c r="F245" t="s">
         <v>317</v>
       </c>
@@ -29137,6 +29870,9 @@
       <c r="D246" t="s">
         <v>425</v>
       </c>
+      <c r="E246" s="2">
+        <v>46230</v>
+      </c>
       <c r="F246" t="s">
         <v>317</v>
       </c>
@@ -29250,6 +29986,9 @@
       <c r="D247" t="s">
         <v>425</v>
       </c>
+      <c r="E247" s="2">
+        <v>46230</v>
+      </c>
       <c r="F247" t="s">
         <v>317</v>
       </c>
@@ -29360,6 +30099,9 @@
       <c r="D248" t="s">
         <v>428</v>
       </c>
+      <c r="E248" s="2">
+        <v>46230</v>
+      </c>
       <c r="F248" t="s">
         <v>317</v>
       </c>
@@ -29470,6 +30212,9 @@
       <c r="D249" t="s">
         <v>428</v>
       </c>
+      <c r="E249" s="2">
+        <v>46230</v>
+      </c>
       <c r="F249" t="s">
         <v>317</v>
       </c>
@@ -29580,6 +30325,9 @@
       <c r="D250" t="s">
         <v>431</v>
       </c>
+      <c r="E250" s="2">
+        <v>46230</v>
+      </c>
       <c r="F250" t="s">
         <v>317</v>
       </c>
@@ -29693,6 +30441,9 @@
       <c r="D251" t="s">
         <v>431</v>
       </c>
+      <c r="E251" s="2">
+        <v>46230</v>
+      </c>
       <c r="F251" t="s">
         <v>317</v>
       </c>
@@ -29803,6 +30554,9 @@
       <c r="D252" t="s">
         <v>434</v>
       </c>
+      <c r="E252" s="2">
+        <v>46230</v>
+      </c>
       <c r="F252" t="s">
         <v>317</v>
       </c>
@@ -29913,6 +30667,9 @@
       <c r="D253" t="s">
         <v>434</v>
       </c>
+      <c r="E253" s="2">
+        <v>46230</v>
+      </c>
       <c r="F253" t="s">
         <v>317</v>
       </c>
@@ -30023,6 +30780,9 @@
       <c r="D254" t="s">
         <v>437</v>
       </c>
+      <c r="E254" s="2">
+        <v>46230</v>
+      </c>
       <c r="F254" t="s">
         <v>317</v>
       </c>
@@ -30136,6 +30896,9 @@
       <c r="D255" t="s">
         <v>437</v>
       </c>
+      <c r="E255" s="2">
+        <v>46230</v>
+      </c>
       <c r="F255" t="s">
         <v>317</v>
       </c>
@@ -30246,6 +31009,9 @@
       <c r="D256" t="s">
         <v>440</v>
       </c>
+      <c r="E256" s="2">
+        <v>46230</v>
+      </c>
       <c r="F256" t="s">
         <v>317</v>
       </c>
@@ -30356,6 +31122,9 @@
       <c r="D257" t="s">
         <v>440</v>
       </c>
+      <c r="E257" s="2">
+        <v>46230</v>
+      </c>
       <c r="F257" t="s">
         <v>317</v>
       </c>
@@ -30466,6 +31235,9 @@
       <c r="D258" t="s">
         <v>443</v>
       </c>
+      <c r="E258" s="2">
+        <v>46230</v>
+      </c>
       <c r="F258" t="s">
         <v>317</v>
       </c>
@@ -30576,6 +31348,9 @@
       <c r="D259" t="s">
         <v>443</v>
       </c>
+      <c r="E259" s="2">
+        <v>46230</v>
+      </c>
       <c r="F259" t="s">
         <v>317</v>
       </c>
@@ -30686,6 +31461,9 @@
       <c r="D260" t="s">
         <v>446</v>
       </c>
+      <c r="E260" s="2">
+        <v>46230</v>
+      </c>
       <c r="F260" t="s">
         <v>317</v>
       </c>
@@ -30796,6 +31574,9 @@
       <c r="D261" t="s">
         <v>446</v>
       </c>
+      <c r="E261" s="2">
+        <v>46230</v>
+      </c>
       <c r="F261" t="s">
         <v>317</v>
       </c>
@@ -30906,6 +31687,9 @@
       <c r="D262" t="s">
         <v>449</v>
       </c>
+      <c r="E262" s="2">
+        <v>46230</v>
+      </c>
       <c r="F262" t="s">
         <v>317</v>
       </c>
@@ -31016,6 +31800,9 @@
       <c r="D263" t="s">
         <v>449</v>
       </c>
+      <c r="E263" s="2">
+        <v>46230</v>
+      </c>
       <c r="F263" t="s">
         <v>317</v>
       </c>
@@ -31126,6 +31913,9 @@
       <c r="D264" t="s">
         <v>452</v>
       </c>
+      <c r="E264" s="2">
+        <v>46230</v>
+      </c>
       <c r="F264" t="s">
         <v>317</v>
       </c>
@@ -31239,6 +32029,9 @@
       <c r="D265" t="s">
         <v>452</v>
       </c>
+      <c r="E265" s="2">
+        <v>46230</v>
+      </c>
       <c r="F265" t="s">
         <v>317</v>
       </c>
@@ -31349,6 +32142,9 @@
       <c r="D266" t="s">
         <v>455</v>
       </c>
+      <c r="E266" s="2">
+        <v>46230</v>
+      </c>
       <c r="F266" t="s">
         <v>317</v>
       </c>
@@ -31461,6 +32257,9 @@
       </c>
       <c r="D267" t="s">
         <v>455</v>
+      </c>
+      <c r="E267" s="2">
+        <v>46230</v>
       </c>
       <c r="F267" t="s">
         <v>317</v>
